--- a/exports/colleges/25992_iit-roorkee-indian-institute-of-technology-iitr-roorkee.xlsx
+++ b/exports/colleges/25992_iit-roorkee-indian-institute-of-technology-iitr-roorkee.xlsx
@@ -445,7 +445,7 @@
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="100" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="171" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #18</t>
+          <t>Not Ranked</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>11.33 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GATE, COAP</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Management</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>3.07 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Post graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.86 Lakhs</t>
+          <t>1.86 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 55% + IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IIT JAM, JOAPS</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 May - 15 Jun 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9.74 Lakhs</t>
+          <t>9.74 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation with 60% + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CAT, GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>9 Jan - 15 Feb 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.33 Lakhs - 14.25 Lakhs</t>
+          <t>14.13 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 June - 18 Jun 2024</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.18 Lakhs - 6.5 Lakhs</t>
+          <t>12.19 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 June - 12 Jun 2025</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.07 Lakhs - 4.42 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.86 Lakhs</t>
+          <t>12.35 L - 14.25 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.74 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Mar - 04 Apr 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Master of Planning (Urban and Regional Planning)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Master of Planning (Urban and Regional Planning)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.13 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>Post Graduate Diploma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>Post Graduate Diploma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.19 Lakhs</t>
+          <t>62,500 - 70,500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Professional Certificate Program in Product Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Professional Certificate Program in Product Management</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>1.4 L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 months</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>Masters in Innovation Management [MIM]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>Masters in Innovation Management [MIM]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Master of Technology [M.Tech] (Seismic Science &amp; Engineering)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Master of Technology [M.Tech] (Seismic Science &amp; Engineering)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4 Lakhs</t>
+          <t>2.18 L</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.68 Lakhs</t>
+          <t>4.42 L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>11.33 L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>14 Mar - 03 Apr 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1746,32 +1746,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Data Science and Artificial Intelligence</t>
+          <t>Master of Technology [M.Tech] (VLSI Design)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Data Science and Artificial Intelligence</t>
+          <t>Master of Technology [M.Tech] (VLSI Design)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>6.5 L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 21 Apr 2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Electronics &amp; Communication Engineering</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Electronics &amp; Communication Engineering</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 75% + JEE Advanced</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GATE</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE, COAP</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1932,27 +1932,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>M.Phil/Ph.D in Management</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>3.07 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post graduation</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>1.86 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 55% + IIT JAM</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>IIT JAM, JOAPS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>9.74 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60% + CAT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>CAT, GMAT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2123,17 +2123,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>11.33 Lakhs - 14.25 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biosciences and Bioengineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Biosciences and Bioengineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>2.18 Lakhs - 6.5 Lakhs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>3.07 Lakhs - 4.42 Lakhs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2304,27 +2304,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11.33 Lakhs</t>
+          <t>1.86 Lakhs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>9.74 Lakhs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2428,27 +2428,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>14.13 Lakhs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2490,27 +2490,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>BS + MS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>BS + MS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>12.19 Lakhs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2676,27 +2676,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Industrial Safety</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Industrial Safety</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>1.4 Lakhs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2738,22 +2738,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pulp &amp; paper Technology</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pulp &amp; paper Technology</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.68 Lakhs</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2800,27 +2800,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hydro and Renewable Energy</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hydro and Renewable Energy</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2862,27 +2862,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Semiconductor Technology</t>
+          <t>Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Semiconductor Technology</t>
+          <t>Data Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2924,27 +2924,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Packaging Technology</t>
+          <t>Electronics &amp; Communication Engineering</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Packaging Technology</t>
+          <t>Electronics &amp; Communication Engineering</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2986,27 +2986,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3048,27 +3048,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Geospatial Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Geospatial Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3110,27 +3110,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hydrology &amp; Water Resources</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hydrology &amp; Water Resources</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3172,27 +3172,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3234,27 +3234,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mechanical &amp; Industrial Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mechanical &amp; Industrial Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAD, CAM &amp; Robotics</t>
+          <t>Biosciences and Bioengineering</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAD, CAM &amp; Robotics</t>
+          <t>Biosciences and Bioengineering</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3358,27 +3358,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Disaster Mitigation &amp; Management</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Disaster Mitigation &amp; Management</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3420,27 +3420,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irrigation Water Management Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Irrigation Water Management Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
+          <t>11.33 Lakhs</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bioprocess</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bioprocess</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Electrical Vehicle Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Electrical Vehicle Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Water Resources Development &amp; Management</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Water Resources Development &amp; Management</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Drinking Water and Sanitation</t>
+          <t>Industrial Safety</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Drinking Water and Sanitation</t>
+          <t>Industrial Safety</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rf And Microwave Engineering</t>
+          <t>Pulp &amp; paper Technology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Rf And Microwave Engineering</t>
+          <t>Pulp &amp; paper Technology</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Structural Dynamics</t>
+          <t>Hydro and Renewable Energy</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Structural Dynamics</t>
+          <t>Hydro and Renewable Energy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Semiconductor Technology</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Semiconductor Technology</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dam Safety and Rehabilitation</t>
+          <t>Packaging Technology</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Dam Safety and Rehabilitation</t>
+          <t>Packaging Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Environmental Management</t>
+          <t>Geospatial Engineering</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Environmental Management</t>
+          <t>Geospatial Engineering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Hydrology &amp; Water Resources</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Hydrology &amp; Water Resources</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Photonic</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Photonic</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Electrical Drives</t>
+          <t>Mechanical &amp; Industrial Engineering</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Electrical Drives</t>
+          <t>Mechanical &amp; Industrial Engineering</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>CAD, CAM &amp; Robotics</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>CAD, CAM &amp; Robotics</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Disaster Mitigation &amp; Management</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Disaster Mitigation &amp; Management</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Computational Biology</t>
+          <t>Irrigation Water Management Engineering</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Computational Biology</t>
+          <t>Irrigation Water Management Engineering</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Instrumentation and Signal Processing</t>
+          <t>Bioprocess</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Instrumentation and Signal Processing</t>
+          <t>Bioprocess</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hydraulics</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hydraulics</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Infrastructure Engineering</t>
+          <t>Nanotechnology</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Infrastructure Engineering</t>
+          <t>Nanotechnology</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Electrical Vehicle Engineering</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Electrical Vehicle Engineering</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Earthquake Engineering</t>
+          <t>Water Resources Development &amp; Management</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Earthquake Engineering</t>
+          <t>Water Resources Development &amp; Management</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Drinking Water and Sanitation</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Drinking Water and Sanitation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additive Manufacturing</t>
+          <t>Rf And Microwave Engineering</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Additive Manufacturing</t>
+          <t>Rf And Microwave Engineering</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Computational Materials Engineering</t>
+          <t>Structural Dynamics</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Computational Materials Engineering</t>
+          <t>Structural Dynamics</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Industrial Metallurgy</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Industrial Metallurgy</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Machine Design</t>
+          <t>Dam Safety and Rehabilitation</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Machine Design</t>
+          <t>Dam Safety and Rehabilitation</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Power System &amp; Control</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Power System &amp; Control</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Production &amp; Industrial Engineering</t>
+          <t>Environmental Management</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Production &amp; Industrial Engineering</t>
+          <t>Environmental Management</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scientific Computing</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Scientific Computing</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Soil Dynamics</t>
+          <t>Photonic</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Soil Dynamics</t>
+          <t>Photonic</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Space Engineering</t>
+          <t>Power Electronics &amp; Electrical Drives</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Space Engineering</t>
+          <t>Power Electronics &amp; Electrical Drives</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sustainable Energy Engineering</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sustainable Energy Engineering</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>System Management</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>System Management</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wireless Communication &amp; Sensor Networks</t>
+          <t>Computational Biology</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wireless Communication &amp; Sensor Networks</t>
+          <t>Computational Biology</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5714,27 +5714,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ph.D Management Studies</t>
+          <t>Instrumentation and Signal Processing</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ph.D Management Studies</t>
+          <t>Instrumentation and Signal Processing</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ph.D Chemistry</t>
+          <t>Hydraulics</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ph.D Chemistry</t>
+          <t>Hydraulics</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5838,27 +5838,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ph.D Humanities And Social Science</t>
+          <t>Infrastructure Engineering</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ph.D Humanities And Social Science</t>
+          <t>Infrastructure Engineering</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5900,27 +5900,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ph.D Mathematics</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ph.D Mathematics</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5962,27 +5962,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ph.D Biosciences and Biomedical Engineering</t>
+          <t>Earthquake Engineering</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ph.D Biosciences and Biomedical Engineering</t>
+          <t>Earthquake Engineering</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6024,27 +6024,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6086,27 +6086,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Additive Manufacturing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Additive Manufacturing</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6148,27 +6148,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Applied Mathematics</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Applied Mathematics</t>
+          <t>Computational Materials Engineering</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Applied Mathematics</t>
+          <t>Computational Materials Engineering</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6210,27 +6210,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Architecture and Planning</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Architecture and Planning</t>
+          <t>Industrial Metallurgy</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Architecture and Planning</t>
+          <t>Industrial Metallurgy</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6272,27 +6272,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Machine Design</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Machine Design</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6334,27 +6334,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hydrology</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hydrology</t>
+          <t>Power System &amp; Control</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hydrology</t>
+          <t>Power System &amp; Control</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6396,27 +6396,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Production &amp; Industrial Engineering</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Production &amp; Industrial Engineering</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6458,27 +6458,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Scientific Computing</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Scientific Computing</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6520,27 +6520,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Soil Dynamics</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Soil Dynamics</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6582,27 +6582,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Disaster Management</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Disaster Management</t>
+          <t>Space Engineering</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Disaster Management</t>
+          <t>Space Engineering</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6644,27 +6644,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Earthquake Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Earthquake Engineering</t>
+          <t>Sustainable Energy Engineering</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Earthquake Engineering</t>
+          <t>Sustainable Energy Engineering</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6706,27 +6706,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>System Management</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>System Management</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6768,27 +6768,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Polymer Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Polymer Engineering</t>
+          <t>Wireless Communication &amp; Sensor Networks</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Polymer Engineering</t>
+          <t>Wireless Communication &amp; Sensor Networks</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3.07 Lakhs</t>
+          <t>2.18 Lakhs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6830,17 +6830,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Ph.D Management Studies</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Ph.D Management Studies</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6892,17 +6892,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Ph.D Chemistry</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Ph.D Chemistry</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6954,17 +6954,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Quantum Electronics</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Quantum Electronics</t>
+          <t>Ph.D Humanities And Social Science</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Quantum Electronics</t>
+          <t>Ph.D Humanities And Social Science</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -7016,17 +7016,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Electronics And Communications Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Electronics And Communications Engineering</t>
+          <t>Ph.D Mathematics</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Electronics And Communications Engineering</t>
+          <t>Ph.D Mathematics</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -7078,17 +7078,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Ph.D Biosciences and Biomedical Engineering</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Ph.D Biosciences and Biomedical Engineering</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -7140,17 +7140,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7202,17 +7202,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7264,17 +7264,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Applied Mathematics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Applied Mathematics</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Applied Mathematics</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Architecture and Planning</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Architecture and Planning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Architecture and Planning</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7388,17 +7388,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Paper Technology</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Paper Technology</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paper Technology</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7450,17 +7450,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Space Technologies</t>
+          <t>Hydrology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Space Technologies</t>
+          <t>Hydrology</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Space Technologies</t>
+          <t>Hydrology</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7512,17 +7512,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sustainable Technologies</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sustainable Technologies</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sustainable Technologies</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7574,17 +7574,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7636,25 +7636,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>M.Sc (General)</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.86 Lakhs</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -7694,27 +7698,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Disaster Management</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Disaster Management</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Disaster Management</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>9.74 Lakhs</t>
+          <t>3.07 Lakhs</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7729,7 +7733,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7744,7 +7748,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -7756,27 +7760,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Earthquake Engineering</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Earthquake Engineering</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Earthquake Engineering</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9.74 Lakhs</t>
+          <t>3.07 Lakhs</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7786,12 +7790,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7806,7 +7810,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -7818,27 +7822,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Renewable Energy</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Renewable Energy</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Renewable Energy</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>9.74 Lakhs</t>
+          <t>3.07 Lakhs</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7848,12 +7852,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7868,7 +7872,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -7880,25 +7884,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Polymer Engineering</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B.Arch (General)</t>
+          <t>Polymer Engineering</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Polymer Engineering</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14.13 Lakhs</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -7938,25 +7946,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BS + MS (General)</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>12.19 Lakhs</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -7996,25 +8008,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>M.Arch (General)</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -8054,25 +8070,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>Quantum Electronics</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>M.Plan (General)</t>
+          <t>Quantum Electronics</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Quantum Electronics</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2.18 Lakhs</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -8112,25 +8132,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Electronics And Communications Engineering</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Certification (General)</t>
+          <t>Electronics And Communications Engineering</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Electronics And Communications Engineering</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.4 Lakhs</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -8170,55 +8194,1147 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>Artificial Intelligence &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Computer Science And Engineering</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Computer Science And Engineering</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Computer Science And Engineering</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Instrumentation and Control</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Instrumentation and Control</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Instrumentation and Control</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Nanotechnology</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Nanotechnology</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nanotechnology</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Paper Technology</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Paper Technology</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Paper Technology</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Space Technologies</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Space Technologies</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Space Technologies</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sustainable Technologies</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Sustainable Technologies</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Sustainable Technologies</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Transportation Engineering</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>M.Sc (General)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1.86 Lakhs</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>9.74 Lakhs</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>9.74 Lakhs</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>9.74 Lakhs</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>B.Arch</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>B.Arch (General)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>14.13 Lakhs</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BS + MS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>BS + MS (General)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>12.19 Lakhs</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>M.Arch</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>M.Arch (General)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2.18 Lakhs</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>M.Plan</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>M.Plan (General)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2.18 Lakhs</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Certification (General)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>25992</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>EMBA</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>EMBA (General)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>11.68 Lakhs</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>2 Years</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
         <is>
           <t>CAT</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -8372,12 +9488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,50,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18,34,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -8407,13 +9523,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8424,17 +9538,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -8446,15 +9550,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #18</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
